--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0033.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0033.xlsx
@@ -3252,7 +3252,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Dùng Outro Skill của Hiyuki 100 lần.</t>
+          <t>Dùng Kỹ Năng Outro của Hiyuki 100 lần.</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Sử dụng Outro Skill của Denia 100 lần.</t>
+          <t>Sử dụng Kỹ Năng Outro của Denia 100 lần.</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Energy Regen Skill</t>
+          <t>Hồi Năng Lượng Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Năng lượng Skill được phục hồi mỗi giây.</t>
+          <t>Năng Lượng Kỹ năng hồi mỗi giây</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Summon một cơn lốc tại vị trí của người chơi để gây sát thương.</t>
+          <t>Triệu hồi một cơn lốc tại vị trí của người chơi để gây DMG.</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Tích năng lượng và nhận Shield trong lúc triệu hồi gai đất truy đuổi và tấn công mục tiêu, gây chậm đáng kể khi trúng đích. Phá vỡ Shield sẽ làm gián đoạn quá trình tích năng và khiến nó bị bất động.</t>
+          <t>Tích năng lượng và nhận Khiên trong lúc triệu hồi gai đất truy đuổi và tấn công mục tiêu, gây chậm đáng kể khi trúng đích. Phá vỡ Khiên sẽ làm gián đoạn quá trình tích năng và khiến nó bị bất động.</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Nhảy lên rồi đập mạnh xuống đất, sau đó dùng cả hai nắm đấm đập xuống gây sát thương.</t>
+          <t>Nhảy lên rồi đập mạnh xuống đất, sau đó dùng cả hai nắm đấm đập xuống gây DMG.</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4292,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Xoay cả hai tay và lao về phía mục tiêu để gây sát thương.</t>
+          <t>Xoay cả hai tay và lao về phía mục tiêu để gây DMG.</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Summon tia sét giáng xuống vị trí mục tiêu.</t>
+          <t>Triệu hồi tia sét giáng xuống vị trí mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4877,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Startorch Academy và Bộ tộc Roya đã hợp tác thiết lập căn cứ tại Dimmr Plains, khởi động chuyến thám hiểm khoa học chung vào vùng đất cô lập từ lâu này. Mục tiêu bao gồm thu thập dữ liệu môi trường, phục hồi mẫu thực vật cổ đại và linh kiện Exostrider, cũng như khắc phục thiệt hại môi trường do Void Storm gây ra. Thành quả của chiến dịch này sẽ thúc đẩy đáng kể nghiên cứu sinh thái và phục hồi môi trường sống tại Lahai-Roi.</t>
+          <t>Học viện Startorch và Bộ tộc Roya đã hợp tác thiết lập căn cứ tại Đồng bằng Dimmr, khởi động chuyến thám hiểm khoa học chung vào vùng đất cô lập từ lâu này. Mục tiêu bao gồm thu thập dữ liệu môi trường, phục hồi mẫu thực vật cổ đại và linh kiện Exostrider, cũng như khắc phục thiệt hại môi trường do Bão Hư Không gây ra. Thành quả của chiến dịch này sẽ thúc đẩy đáng kể nghiên cứu sinh thái và phục hồi môi trường sống tại Lahai-Roi.</t>
         </is>
       </c>
     </row>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Glacio DMG+</t>
+          <t>Tăng Sát Thương Glacio</t>
         </is>
       </c>
     </row>
@@ -5010,9 +5010,9 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Gây Trầy Băng Giá sẽ trao thưởng Sát Thương Băng Giá và hiệu ứng Tuyết Rơi:
+          <t>Gây Glacio Chafe sẽ trao thưởng Sát Thương Băng Giá và hiệu ứng Tuyết Rơi:
 - Gây Sát Thương Resonance Liberation sẽ loại bỏ Tuyết Rơi và tăng Crit. Rate.
-- Sử dụng Outro Skill sẽ loại bỏ Tuyết Rơi và trao thưởng Sát Thương Băng Giá cho Resonator tiếp theo.
+- Sử dụng Kỹ Năng Outro sẽ loại bỏ Tuyết Rơi và trao thưởng Sát Thương Băng Giá cho Resonator tiếp theo.
 Khi Tuyết Rơi bị loại bỏ, chỉ một trong hai hiệu ứng trên có thể được kích hoạt.</t>
         </is>
       </c>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Tấn Công+</t>
+          <t>ATK+</t>
         </is>
       </c>
     </row>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Gây Hiệu Ứng Vỡ Giai Tune: Dịch Chuyển hoặc Căng Giai Tune: Dịch Chuyển lên kẻ địch sẽ tăng Tăng Cường Tune Break cho Resonators trong đội. Hiệu ứng cùng tên không cộng dồn.</t>
+          <t>Gây Hiệu Ứng Vỡ Giai Điệu: Shifting or Tune Strain: Shifting on enemies increases the Tune Break Boost for Resonators in the team. Effects of the same name do not stack.</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Cập nhật Tương tác Chế độ Cộng hưởng</t>
+          <t>Cập Nhật Tương Tác Chế Độ Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Hiển thị và chuyển đổi Resonance Mode giờ đây có thể truy cập trực tiếp từ một số giao diện trong trò chơi.</t>
+          <t>Hiển thị và chuyển đổi Chế Độ Cộng Hưởng giờ đây có thể truy cập trực tiếp từ một số giao diện trong trò chơi.</t>
         </is>
       </c>
     </row>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Cập nhật Tương tác Chế độ Cộng hưởng</t>
+          <t>Cập Nhật Tương Tác Chế Độ Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Khi mục tiêu bị &lt;color=Highlight&gt;Glacio Bite&lt;/color&gt;, hiệu ứng sẽ kích hoạt dựa trên giới hạn stack tối đa hiện tại. Có thể gây &lt;color=Highlight&gt;Glacio Bite&lt;/color&gt; lên mục tiêu đang &lt;color=Highlight&gt;đóng băng&lt;/color&gt;. &lt;color=Highlight&gt;Glacio Bite&lt;/color&gt; cũng được coi là &lt;color=Highlight&gt;Glacio Chafe&lt;/color&gt; và &lt;color=Highlight&gt;Glacio DMG Bite&lt;/color&gt; cũng được tính là &lt;color=Highlight&gt;Glacio DMG Chafe&lt;/color&gt;.</t>
+          <t>Khi mục tiêu bị &lt;color=Highlight&gt;Glacio Bite&lt;/color&gt;, hiệu ứng sẽ kích hoạt dựa trên giới hạn stack tối đa hiện tại. Có thể gây &lt;color=Highlight&gt;Glacio Bite&lt;/color&gt; lên mục tiêu đang &lt;color=Highlight&gt;đóng băng&lt;/color&gt;. &lt;color=Highlight&gt;Glacio Bite&lt;/color&gt; cũng được coi là &lt;color=Highlight&gt;Glacio Chafe&lt;/color&gt; và &lt;color=Highlight&gt;Sát Thương Glacio Bite&lt;/color&gt; cũng được tính là &lt;color=Highlight&gt;Sát Thương Glacio Chafe&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Tăng DMG Skill.</t>
+          <t>DMG Kỹ năng tăng lên.</t>
         </is>
       </c>
     </row>
